--- a/wb.xlsx
+++ b/wb.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Market Correction Panic</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bank &amp; Auto-Debit Friction</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Directionless Onboarding</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Platform Bugs</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Same-Category Overlap</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Market Correction Panic</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bank &amp; Auto-Debit Friction</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Directionless Onboarding</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Platform Bugs</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Market Correction Panic</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bank &amp; Auto-Debit Friction</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Directionless Onboarding</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Platform Bugs</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Same-Category Overlap</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Market Correction Panic</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Bank &amp; Auto-Debit Friction</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Directionless Onboarding</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Platform Bugs</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Market Correction Panic</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Bank &amp; Auto-Debit Friction</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Directionless Onboarding</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Platform Bugs</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Same-Category Overlap</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Market Correction Panic</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Bank &amp; Auto-Debit Friction</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Directionless Onboarding</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Platform Bugs</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Market Correction Panic</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Bank &amp; Auto-Debit Friction</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Directionless Onboarding</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Platform Bugs</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Same-Category Overlap</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Market Correction Panic</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Bank &amp; Auto-Debit Friction</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Directionless Onboarding</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -9274,7 +9274,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Platform Bugs</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Market Correction Panic</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Bank &amp; Auto-Debit Friction</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Directionless Onboarding</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -10394,7 +10394,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Platform Bugs</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -10954,7 +10954,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Same-Category Overlap</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Market Correction Panic</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Bank &amp; Auto-Debit Friction</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Directionless Onboarding</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -11584,7 +11584,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Platform Bugs</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Market Correction Panic</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Bank &amp; Auto-Debit Friction</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Directionless Onboarding</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Platform Bugs</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Same-Category Overlap</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Market Correction Panic</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -13334,7 +13334,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Bank &amp; Auto-Debit Friction</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Directionless Onboarding</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -13684,7 +13684,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Platform Bugs</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Market Correction Panic</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -14314,7 +14314,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -14384,7 +14384,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -14454,7 +14454,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Bank &amp; Auto-Debit Friction</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -14664,7 +14664,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -14734,7 +14734,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Directionless Onboarding</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Platform Bugs</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -14944,7 +14944,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -15014,7 +15014,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -15084,7 +15084,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Same-Category Overlap</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Market Correction Panic</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -15574,7 +15574,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -15644,7 +15644,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Bank &amp; Auto-Debit Friction</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Directionless Onboarding</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -15854,7 +15854,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -15924,7 +15924,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -15994,7 +15994,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Liquidity Shortage</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Platform Bugs</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Platform Bugs</t>
+          <t>Disappointment Valley</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -16204,7 +16204,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Disappointment Valley</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Same-Category Overlap</t>
+          <t>Market Correction Panic</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Directionless Onboarding</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -16484,7 +16484,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Liquidity Shortage</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -16554,7 +16554,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Market Correction Panic</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -16624,7 +16624,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Social Influence</t>
+          <t>Bank &amp; Auto-Debit Friction</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">

--- a/wb.xlsx
+++ b/wb.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Panic/Fear</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Anxiety/Stress</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Distrust</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Anxiety/Stress</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mature (M15+)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Panic/Fear</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Distrust</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Panic/Fear</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Anxiety/Stress</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Distrust</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Anxiety/Stress</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mature (M15+)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Panic/Fear</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Distrust</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Panic/Fear</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Anxiety/Stress</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Distrust</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Anxiety/Stress</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Mature (M15+)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Panic/Fear</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Distrust</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Panic/Fear</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Anxiety/Stress</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Distrust</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Anxiety/Stress</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Mature (M15+)</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Panic/Fear</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Distrust</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Panic/Fear</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10319,7 +10319,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Anxiety/Stress</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Distrust</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Anxiety/Stress</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mature (M15+)</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Panic/Fear</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11089,7 +11089,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Distrust</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Panic/Fear</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12209,7 +12209,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -12559,7 +12559,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Anxiety/Stress</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Distrust</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -12699,7 +12699,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -12859,7 +12859,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Anxiety/Stress</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13189,7 +13189,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mature (M15+)</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -13209,7 +13209,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13259,7 +13259,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Panic/Fear</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13469,7 +13469,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -13749,7 +13749,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -13819,7 +13819,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Distrust</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -13889,7 +13889,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -13979,7 +13979,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Panic/Fear</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14169,7 +14169,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -14309,7 +14309,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -14469,7 +14469,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -14589,7 +14589,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -14609,7 +14609,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -14729,7 +14729,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -14799,7 +14799,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Anxiety/Stress</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -14869,7 +14869,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Distrust</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -15029,7 +15029,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15079,7 +15079,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -15099,7 +15099,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -15169,7 +15169,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -15239,7 +15239,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15359,7 +15359,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>Anxiety/Stress</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -15429,7 +15429,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Mature (M15+)</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -15499,7 +15499,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -15519,7 +15519,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Panic/Fear</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -15569,7 +15569,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -15659,7 +15659,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -15709,7 +15709,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -15779,7 +15779,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Aimlessness</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -15849,7 +15849,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -15869,7 +15869,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -15919,7 +15919,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -15989,7 +15989,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Overwhelm</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16059,7 +16059,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Distrust</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16129,7 +16129,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Cliff (M10-14)</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Distrust</t>
+          <t>Disillusionment</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -16219,7 +16219,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Disillusionment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -16289,7 +16289,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Anger/Resentment</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Mid SIP (M4-9)</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -16359,7 +16359,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Overwhelm</t>
+          <t>Panic/Fear</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -16429,7 +16429,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Aimlessness</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -16549,7 +16549,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>At Risk</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Panic/Fear</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Paused</t>
+          <t>Early SIP (M1-3)</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>Peer comparison</t>
+          <t>Anxiety/Stress</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">

--- a/wb.xlsx
+++ b/wb.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12869,7 +12869,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14059,7 +14059,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14129,7 +14129,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14479,7 +14479,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14759,7 +14759,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15109,7 +15109,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15179,7 +15179,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15319,7 +15319,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15389,7 +15389,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15669,7 +15669,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15879,7 +15879,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16159,7 +16159,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>SIP status reliability fixes + transparent instalment lifecycle tracker</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>‘Your SIP in Context’ card: historical rolling-return ranges + units accumulated</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Pre-Debit Balance Predictor (T-3 day alert + 1-tap date shift) and Mandate Health Check</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16369,7 +16369,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Same-Category Overlap Consolidator: category overlap insight + guided merge flow</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16439,7 +16439,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Goal-anchored SIP setup with neutral milestone progress check-ins at M3, M6, M9, M12</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>SIP Sabbatical: pause 1–3 instalments or step down amount instead of cancelling</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16579,7 +16579,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Calm-Market Context: historical drawdown-and-recovery ranges and unit accumulation context</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Education module on holding period outcomes and switching costs</t>
+          <t>Proactive guidance and communication</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">

--- a/wb.xlsx
+++ b/wb.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12869,7 +12869,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14059,7 +14059,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14129,7 +14129,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14479,7 +14479,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14759,7 +14759,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15109,7 +15109,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15179,7 +15179,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15319,7 +15319,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15389,7 +15389,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15669,7 +15669,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15879,7 +15879,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16159,7 +16159,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16369,7 +16369,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16439,7 +16439,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16579,7 +16579,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Proactive guidance and communication</t>
+          <t>Proactive communication and guidance</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">

--- a/wb.xlsx
+++ b/wb.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N232"/>
+  <dimension ref="A1:M232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,12 +479,7 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Recommended Groww Intervention</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Target North-Star Metric Impact</t>
+          <t>Year</t>
         </is>
       </c>
     </row>
@@ -547,16 +542,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -617,16 +603,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -687,16 +664,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -757,16 +725,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -827,16 +786,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -897,16 +847,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -967,16 +908,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1037,16 +969,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1107,16 +1030,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1177,16 +1091,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1247,16 +1152,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1317,16 +1213,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1387,15 +1274,8 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
+      <c r="M14" t="n">
+        <v>2020</v>
       </c>
     </row>
     <row r="15">
@@ -1457,16 +1337,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1527,16 +1398,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1597,16 +1459,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1667,16 +1520,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1737,16 +1581,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1807,16 +1642,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1877,16 +1703,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1947,16 +1764,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2017,16 +1825,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2087,16 +1886,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2157,16 +1947,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2227,16 +2008,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2297,16 +2069,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2367,16 +2130,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2437,16 +2191,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2507,16 +2252,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2577,16 +2313,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2647,16 +2374,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2717,16 +2435,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2787,16 +2496,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2857,16 +2557,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2927,16 +2618,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2997,16 +2679,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3067,16 +2740,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3137,16 +2801,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3207,16 +2862,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3277,16 +2923,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3347,16 +2984,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3417,16 +3045,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3487,16 +3106,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3557,16 +3167,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3627,15 +3228,8 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
+      <c r="M46" t="n">
+        <v>2020</v>
       </c>
     </row>
     <row r="47">
@@ -3697,16 +3291,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3767,16 +3352,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3837,16 +3413,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3907,16 +3474,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3977,16 +3535,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4047,16 +3596,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4117,16 +3657,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4187,16 +3718,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4257,16 +3779,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4327,16 +3840,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4397,16 +3901,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4467,16 +3962,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4537,16 +4023,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4607,16 +4084,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4677,16 +4145,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4747,16 +4206,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4817,16 +4267,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4887,16 +4328,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4957,16 +4389,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5027,16 +4450,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5097,16 +4511,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5167,16 +4572,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5237,16 +4633,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5307,16 +4694,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5377,16 +4755,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5447,16 +4816,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5517,16 +4877,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5587,16 +4938,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5657,16 +4999,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5727,16 +5060,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5797,16 +5121,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5867,15 +5182,8 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
+      <c r="M78" t="n">
+        <v>2020</v>
       </c>
     </row>
     <row r="79">
@@ -5937,16 +5245,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6007,16 +5306,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6077,16 +5367,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6147,16 +5428,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6217,16 +5489,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6287,16 +5550,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6357,16 +5611,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6427,16 +5672,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6497,16 +5733,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6567,16 +5794,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6637,16 +5855,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6707,16 +5916,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6777,16 +5977,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6847,16 +6038,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6917,16 +6099,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6987,16 +6160,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7057,16 +6221,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7127,16 +6282,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7197,16 +6343,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7267,16 +6404,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7337,16 +6465,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7407,16 +6526,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7477,16 +6587,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7547,16 +6648,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7617,16 +6709,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7687,16 +6770,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7757,16 +6831,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7827,16 +6892,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7897,16 +6953,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7967,16 +7014,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8037,16 +7075,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8107,15 +7136,8 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
+      <c r="M110" t="n">
+        <v>2020</v>
       </c>
     </row>
     <row r="111">
@@ -8177,16 +7199,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8247,16 +7260,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8317,16 +7321,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8387,16 +7382,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8457,16 +7443,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8527,16 +7504,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8597,16 +7565,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8667,16 +7626,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8737,16 +7687,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8807,16 +7748,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8877,16 +7809,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8947,16 +7870,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9017,16 +7931,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9087,16 +7992,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9157,16 +8053,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9227,16 +8114,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9297,16 +8175,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9367,16 +8236,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9437,16 +8297,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9507,16 +8358,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9577,16 +8419,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9647,16 +8480,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9717,16 +8541,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9787,16 +8602,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9857,16 +8663,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9927,16 +8724,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9997,16 +8785,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10067,16 +8846,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -10137,16 +8907,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10207,16 +8968,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -10277,16 +9029,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10347,15 +9090,8 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
+      <c r="M142" t="n">
+        <v>2020</v>
       </c>
     </row>
     <row r="143">
@@ -10417,16 +9153,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10487,16 +9214,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10557,16 +9275,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10627,16 +9336,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10697,16 +9397,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10767,16 +9458,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10837,16 +9519,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10907,16 +9580,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10977,16 +9641,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -11047,16 +9702,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -11117,16 +9763,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -11187,16 +9824,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -11257,16 +9885,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -11327,16 +9946,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -11397,16 +10007,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -11467,16 +10068,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -11537,16 +10129,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -11607,16 +10190,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11677,16 +10251,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11747,16 +10312,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11817,16 +10373,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11887,16 +10434,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11957,16 +10495,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -12027,16 +10556,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -12097,16 +10617,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -12167,16 +10678,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -12237,16 +10739,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -12307,16 +10800,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -12377,16 +10861,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -12447,16 +10922,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -12517,16 +10983,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -12587,15 +11044,8 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
+      <c r="M174" t="n">
+        <v>2020</v>
       </c>
     </row>
     <row r="175">
@@ -12657,16 +11107,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -12727,16 +11168,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -12797,16 +11229,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N177" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -12867,16 +11290,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -12937,16 +11351,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -13007,16 +11412,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -13077,16 +11473,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -13147,16 +11534,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -13217,16 +11595,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -13287,16 +11656,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -13357,16 +11717,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -13427,16 +11778,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -13497,16 +11839,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -13567,16 +11900,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -13637,16 +11961,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N189" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -13707,16 +12022,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -13777,16 +12083,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N191" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -13847,16 +12144,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N192" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -13917,16 +12205,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -13987,16 +12266,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -14057,16 +12327,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N195" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -14127,16 +12388,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -14197,16 +12449,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N197" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -14267,16 +12510,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -14337,16 +12571,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -14407,16 +12632,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -14477,16 +12693,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N201" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -14547,16 +12754,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -14617,16 +12815,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -14687,16 +12876,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -14757,16 +12937,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N205" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -14827,15 +12998,8 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
+      <c r="M206" t="n">
+        <v>2020</v>
       </c>
     </row>
     <row r="207">
@@ -14897,16 +13061,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -14967,16 +13122,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -15037,16 +13183,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N209" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -15107,16 +13244,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -15177,16 +13305,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -15247,16 +13366,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N212" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -15317,16 +13427,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -15387,16 +13488,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -15457,16 +13549,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -15527,16 +13610,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N216" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -15597,16 +13671,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N217" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -15667,16 +13732,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N218" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -15737,16 +13793,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N219" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -15807,16 +13854,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -15877,16 +13915,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -15947,16 +13976,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N222" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -16017,16 +14037,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -16087,16 +14098,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -16157,16 +14159,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>↓ SIP-related tickets; ↑ CSAT; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -16227,16 +14220,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N226" t="inlineStr">
-        <is>
-          <t>↑ Month-12 SIP retention; ↓ cancellations in M10–14</t>
-        </is>
-      </c>
+      <c r="M226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -16297,16 +14281,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N227" t="inlineStr">
-        <is>
-          <t>↑ SIP instalment success rate; ↓ involuntary SIP failures</t>
-        </is>
-      </c>
+      <c r="M227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -16367,16 +14342,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N228" t="inlineStr">
-        <is>
-          <t>↑ Consolidated (not cancelled) SIP amount; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -16437,16 +14403,7 @@
           <t>High – Product/UX Fix</t>
         </is>
       </c>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N229" t="inlineStr">
-        <is>
-          <t>↑ % of SIPs linked to a goal; ↑ M12 SIP retention</t>
-        </is>
-      </c>
+      <c r="M229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -16507,16 +14464,7 @@
           <t>High – FinTech Nudge</t>
         </is>
       </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N230" t="inlineStr">
-        <is>
-          <t>↑ Pause-instead-of-cancel ratio; ↑ SIP reactivation rate</t>
-        </is>
-      </c>
+      <c r="M230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -16577,16 +14525,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N231" t="inlineStr">
-        <is>
-          <t>↓ SIP stops during &gt;5% drawdown weeks; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -16647,16 +14586,7 @@
           <t>Medium – Investor Education</t>
         </is>
       </c>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>Proactive communication and guidance</t>
-        </is>
-      </c>
-      <c r="N232" t="inlineStr">
-        <is>
-          <t>↓ SIP-to-trading cannibalisation; ↑ M12 retention</t>
-        </is>
-      </c>
+      <c r="M232" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/wb.xlsx
+++ b/wb.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -661,7 +661,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -783,7 +783,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -844,7 +844,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M78" t="n">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -5791,7 +5791,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M110" t="n">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M117" t="inlineStr"/>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
@@ -8599,7 +8599,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M135" t="inlineStr"/>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M141" t="inlineStr"/>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M142" t="n">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M143" t="inlineStr"/>
@@ -9211,7 +9211,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M144" t="inlineStr"/>
@@ -9272,7 +9272,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M146" t="inlineStr"/>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M147" t="inlineStr"/>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M148" t="inlineStr"/>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M149" t="inlineStr"/>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M150" t="inlineStr"/>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M151" t="inlineStr"/>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M152" t="inlineStr"/>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M153" t="inlineStr"/>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M154" t="inlineStr"/>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M156" t="inlineStr"/>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M157" t="inlineStr"/>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M158" t="inlineStr"/>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M159" t="inlineStr"/>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M160" t="inlineStr"/>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
@@ -10309,7 +10309,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M162" t="inlineStr"/>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M163" t="inlineStr"/>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M164" t="inlineStr"/>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M165" t="inlineStr"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M166" t="inlineStr"/>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M167" t="inlineStr"/>
@@ -10675,7 +10675,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M168" t="inlineStr"/>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M169" t="inlineStr"/>
@@ -10797,7 +10797,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M170" t="inlineStr"/>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M171" t="inlineStr"/>
@@ -10919,7 +10919,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M172" t="inlineStr"/>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M173" t="inlineStr"/>
@@ -11041,7 +11041,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M174" t="n">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M175" t="inlineStr"/>
@@ -11165,7 +11165,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M176" t="inlineStr"/>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M177" t="inlineStr"/>
@@ -11287,7 +11287,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M178" t="inlineStr"/>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M179" t="inlineStr"/>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M180" t="inlineStr"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M181" t="inlineStr"/>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M182" t="inlineStr"/>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M183" t="inlineStr"/>
@@ -11653,7 +11653,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M184" t="inlineStr"/>
@@ -11714,7 +11714,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M185" t="inlineStr"/>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M186" t="inlineStr"/>
@@ -11836,7 +11836,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M187" t="inlineStr"/>
@@ -11897,7 +11897,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M188" t="inlineStr"/>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M189" t="inlineStr"/>
@@ -12019,7 +12019,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M190" t="inlineStr"/>
@@ -12080,7 +12080,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M191" t="inlineStr"/>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M192" t="inlineStr"/>
@@ -12202,7 +12202,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M193" t="inlineStr"/>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M194" t="inlineStr"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M195" t="inlineStr"/>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M196" t="inlineStr"/>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M197" t="inlineStr"/>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M198" t="inlineStr"/>
@@ -12568,7 +12568,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M199" t="inlineStr"/>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M200" t="inlineStr"/>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M201" t="inlineStr"/>
@@ -12751,7 +12751,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M202" t="inlineStr"/>
@@ -12812,7 +12812,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M203" t="inlineStr"/>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M204" t="inlineStr"/>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M205" t="inlineStr"/>
@@ -12995,7 +12995,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M206" t="n">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M207" t="inlineStr"/>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M208" t="inlineStr"/>
@@ -13180,7 +13180,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M209" t="inlineStr"/>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M210" t="inlineStr"/>
@@ -13302,7 +13302,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M211" t="inlineStr"/>
@@ -13363,7 +13363,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M212" t="inlineStr"/>
@@ -13424,7 +13424,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M213" t="inlineStr"/>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M214" t="inlineStr"/>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M215" t="inlineStr"/>
@@ -13607,7 +13607,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M216" t="inlineStr"/>
@@ -13668,7 +13668,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M217" t="inlineStr"/>
@@ -13729,7 +13729,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M218" t="inlineStr"/>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M219" t="inlineStr"/>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M220" t="inlineStr"/>
@@ -13912,7 +13912,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M221" t="inlineStr"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M222" t="inlineStr"/>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M223" t="inlineStr"/>
@@ -14095,7 +14095,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M224" t="inlineStr"/>
@@ -14156,7 +14156,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M225" t="inlineStr"/>
@@ -14217,7 +14217,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M226" t="inlineStr"/>
@@ -14278,7 +14278,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M227" t="inlineStr"/>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M228" t="inlineStr"/>
@@ -14400,7 +14400,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>High – Product/UX Fix</t>
+          <t>High - Product UX fix</t>
         </is>
       </c>
       <c r="M229" t="inlineStr"/>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>High – FinTech Nudge</t>
+          <t>High - FinTech Nudge</t>
         </is>
       </c>
       <c r="M230" t="inlineStr"/>
@@ -14522,7 +14522,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M231" t="inlineStr"/>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>Medium – Investor Education</t>
+          <t>Medium - Investor Education</t>
         </is>
       </c>
       <c r="M232" t="inlineStr"/>
